--- a/artfynd/A 43083-2025 artfynd.xlsx
+++ b/artfynd/A 43083-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129166636</v>
       </c>
       <c r="B2" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129167601</v>
       </c>
       <c r="B3" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>129164207</v>
       </c>
       <c r="B4" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>129168008</v>
       </c>
       <c r="B5" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>129167558</v>
       </c>
       <c r="B6" t="n">
-        <v>91299</v>
+        <v>91305</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>129165933</v>
       </c>
       <c r="B7" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>129169685</v>
       </c>
       <c r="B8" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>129166612</v>
       </c>
       <c r="B9" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>129167896</v>
       </c>
       <c r="B10" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,45 +1691,61 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129166637</v>
+        <v>129169688</v>
       </c>
       <c r="B11" t="n">
-        <v>92819</v>
+        <v>57725</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rötjärnshöljan, Rötjärnshöljan, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>504144</v>
+        <v>504135</v>
       </c>
       <c r="R11" t="n">
-        <v>6643441</v>
+        <v>6643675</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1761,7 +1777,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1771,7 +1787,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1798,61 +1814,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129169688</v>
+        <v>129166637</v>
       </c>
       <c r="B12" t="n">
-        <v>57723</v>
+        <v>92826</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Rötjärnshöljan, Rötjärnshöljan, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>504135</v>
+        <v>504144</v>
       </c>
       <c r="R12" t="n">
-        <v>6643675</v>
+        <v>6643441</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1884,7 +1884,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1924,7 +1924,7 @@
         <v>129166514</v>
       </c>
       <c r="B13" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 43083-2025 artfynd.xlsx
+++ b/artfynd/A 43083-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>129167601</v>
       </c>
       <c r="B3" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>129164207</v>
       </c>
       <c r="B4" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,53 +1010,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129168008</v>
+        <v>129167558</v>
       </c>
       <c r="B5" t="n">
-        <v>57725</v>
+        <v>91312</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>3215</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Svarthöljsbäcken, Svarthöljsbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>504320</v>
+        <v>504230</v>
       </c>
       <c r="R5" t="n">
-        <v>6643685</v>
+        <v>6643608</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1085,7 +1080,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,12 +1090,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:02</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Äldre tretåhack på tall.</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,57 +1105,57 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129167558</v>
+        <v>129166612</v>
       </c>
       <c r="B6" t="n">
-        <v>91305</v>
+        <v>79039</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3215</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Svarthöljsbäcken, Svarthöljsbäcken, Vstm</t>
+          <t>Rötjärnshöljan, Rötjärnshöljan, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>504230</v>
+        <v>504081</v>
       </c>
       <c r="R6" t="n">
-        <v>6643608</v>
+        <v>6643500</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1197,7 +1187,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1207,7 +1197,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1234,50 +1224,54 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129165933</v>
+        <v>129167896</v>
       </c>
       <c r="B7" t="n">
-        <v>57722</v>
+        <v>92833</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Rötjärnshöljan, Rötjärnshöljan, Vstm</t>
+          <t>Svarthöljsbäcken, Svarthöljsbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>503875</v>
+        <v>504412</v>
       </c>
       <c r="R7" t="n">
-        <v>6643308</v>
+        <v>6643679</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1309,7 +1303,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1319,12 +1313,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:49</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Födohack av spillkråka på stående grov död tall.</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,50 +1340,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129169685</v>
+        <v>129166637</v>
       </c>
       <c r="B8" t="n">
-        <v>57885</v>
+        <v>92833</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Svarthöljsbäcken, Svarthöljsbäcken, Vstm</t>
+          <t>Rötjärnshöljan, Rötjärnshöljan, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>504320</v>
+        <v>504144</v>
       </c>
       <c r="R8" t="n">
-        <v>6643685</v>
+        <v>6643441</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1426,7 +1410,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1436,12 +1420,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:38</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2 st varningsläte.</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1456,19 +1435,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129166612</v>
+        <v>129166514</v>
       </c>
       <c r="B9" t="n">
         <v>79039</v>
@@ -1497,19 +1476,22 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rötjärnshöljan, Rötjärnshöljan, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>504081</v>
+        <v>503940</v>
       </c>
       <c r="R9" t="n">
-        <v>6643500</v>
+        <v>6643425</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1538,7 +1520,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1548,7 +1530,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På gammal kjolgran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1557,60 +1544,57 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129167896</v>
+        <v>129168008</v>
       </c>
       <c r="B10" t="n">
-        <v>92826</v>
+        <v>57725</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1619,10 +1603,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>504412</v>
+        <v>504320</v>
       </c>
       <c r="R10" t="n">
-        <v>6643679</v>
+        <v>6643685</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1654,7 +1638,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1664,7 +1648,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre tretåhack på tall.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1691,10 +1680,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129169688</v>
+        <v>129165933</v>
       </c>
       <c r="B11" t="n">
-        <v>57725</v>
+        <v>57722</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1702,16 +1691,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1720,32 +1709,21 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rötjärnshöljan, Rötjärnshöljan, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>504135</v>
+        <v>503875</v>
       </c>
       <c r="R11" t="n">
-        <v>6643675</v>
+        <v>6643308</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1777,7 +1755,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1787,7 +1765,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Födohack av spillkråka på stående grov död tall.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1802,57 +1785,62 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129166637</v>
+        <v>129169685</v>
       </c>
       <c r="B12" t="n">
-        <v>92826</v>
+        <v>57885</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Rötjärnshöljan, Rötjärnshöljan, Vstm</t>
+          <t>Svarthöljsbäcken, Svarthöljsbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>504144</v>
+        <v>504320</v>
       </c>
       <c r="R12" t="n">
-        <v>6643441</v>
+        <v>6643685</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1884,7 +1872,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1894,7 +1882,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>2 st varningsläte.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1909,22 +1902,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129166514</v>
+        <v>129169688</v>
       </c>
       <c r="B13" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1932,26 +1925,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1959,10 +1965,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>503940</v>
+        <v>504135</v>
       </c>
       <c r="R13" t="n">
-        <v>6643425</v>
+        <v>6643675</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1994,7 +2000,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2004,12 +2010,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:57</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På gammal kjolgran.</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2018,19 +2019,18 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 43083-2025 artfynd.xlsx
+++ b/artfynd/A 43083-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129166636</v>
       </c>
       <c r="B2" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129167601</v>
       </c>
       <c r="B3" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>129164207</v>
       </c>
       <c r="B4" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>129167558</v>
       </c>
       <c r="B5" t="n">
-        <v>91312</v>
+        <v>91314</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>129166612</v>
       </c>
       <c r="B6" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>129167896</v>
       </c>
       <c r="B7" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>129166637</v>
       </c>
       <c r="B8" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>129166514</v>
       </c>
       <c r="B9" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>129168008</v>
       </c>
       <c r="B10" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>129165933</v>
       </c>
       <c r="B11" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>129169685</v>
       </c>
       <c r="B12" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         <v>129169688</v>
       </c>
       <c r="B13" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 43083-2025 artfynd.xlsx
+++ b/artfynd/A 43083-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>129167601</v>
       </c>
       <c r="B3" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>129164207</v>
       </c>
       <c r="B4" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>129167558</v>
       </c>
       <c r="B5" t="n">
-        <v>91314</v>
+        <v>91313</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>129167896</v>
       </c>
       <c r="B7" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>129166637</v>
       </c>
       <c r="B8" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 43083-2025 artfynd.xlsx
+++ b/artfynd/A 43083-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>129167601</v>
       </c>
       <c r="B3" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>129167896</v>
       </c>
       <c r="B7" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>129166637</v>
       </c>
       <c r="B8" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 43083-2025 artfynd.xlsx
+++ b/artfynd/A 43083-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129166636</v>
       </c>
       <c r="B2" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129167601</v>
       </c>
       <c r="B3" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>129164207</v>
       </c>
       <c r="B4" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>129167558</v>
       </c>
       <c r="B5" t="n">
-        <v>91313</v>
+        <v>91316</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>129166612</v>
       </c>
       <c r="B6" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>129167896</v>
       </c>
       <c r="B7" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>129166637</v>
       </c>
       <c r="B8" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>129166514</v>
       </c>
       <c r="B9" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 43083-2025 artfynd.xlsx
+++ b/artfynd/A 43083-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129166636</v>
       </c>
       <c r="B2" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129167601</v>
       </c>
       <c r="B3" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>129164207</v>
       </c>
       <c r="B4" t="n">
-        <v>91507</v>
+        <v>91509</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>129167558</v>
       </c>
       <c r="B5" t="n">
-        <v>91316</v>
+        <v>91318</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>129166612</v>
       </c>
       <c r="B6" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>129167896</v>
       </c>
       <c r="B7" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>129166637</v>
       </c>
       <c r="B8" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>129166514</v>
       </c>
       <c r="B9" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 43083-2025 artfynd.xlsx
+++ b/artfynd/A 43083-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>129167601</v>
       </c>
       <c r="B3" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>129164207</v>
       </c>
       <c r="B4" t="n">
-        <v>91509</v>
+        <v>91513</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>129167558</v>
       </c>
       <c r="B5" t="n">
-        <v>91318</v>
+        <v>91322</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>129167896</v>
       </c>
       <c r="B7" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>129166637</v>
       </c>
       <c r="B8" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 43083-2025 artfynd.xlsx
+++ b/artfynd/A 43083-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>129167601</v>
       </c>
       <c r="B3" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>129164207</v>
       </c>
       <c r="B4" t="n">
-        <v>91513</v>
+        <v>91514</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>129167558</v>
       </c>
       <c r="B5" t="n">
-        <v>91322</v>
+        <v>91323</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>129167896</v>
       </c>
       <c r="B7" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>129166637</v>
       </c>
       <c r="B8" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 43083-2025 artfynd.xlsx
+++ b/artfynd/A 43083-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>129167601</v>
       </c>
       <c r="B3" t="n">
-        <v>92832</v>
+        <v>92835</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>129164207</v>
       </c>
       <c r="B4" t="n">
-        <v>91514</v>
+        <v>91517</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>129167558</v>
       </c>
       <c r="B5" t="n">
-        <v>91323</v>
+        <v>91326</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>129167896</v>
       </c>
       <c r="B7" t="n">
-        <v>92832</v>
+        <v>92835</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>129166637</v>
       </c>
       <c r="B8" t="n">
-        <v>92832</v>
+        <v>92835</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 43083-2025 artfynd.xlsx
+++ b/artfynd/A 43083-2025 artfynd.xlsx
@@ -1680,10 +1680,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129165933</v>
+        <v>129169685</v>
       </c>
       <c r="B11" t="n">
-        <v>57724</v>
+        <v>57887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1691,39 +1691,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rötjärnshöljan, Rötjärnshöljan, Vstm</t>
+          <t>Svarthöljsbäcken, Svarthöljsbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>503875</v>
+        <v>504320</v>
       </c>
       <c r="R11" t="n">
-        <v>6643308</v>
+        <v>6643685</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1765,12 +1765,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Födohack av spillkråka på stående grov död tall.</t>
+          <t>2 st varningsläte.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1797,10 +1797,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129169685</v>
+        <v>129165933</v>
       </c>
       <c r="B12" t="n">
-        <v>57887</v>
+        <v>57724</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1808,39 +1808,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Svarthöljsbäcken, Svarthöljsbäcken, Vstm</t>
+          <t>Rötjärnshöljan, Rötjärnshöljan, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>504320</v>
+        <v>503875</v>
       </c>
       <c r="R12" t="n">
-        <v>6643685</v>
+        <v>6643308</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2 st varningsläte.</t>
+          <t>Födohack av spillkråka på stående grov död tall.</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 43083-2025 artfynd.xlsx
+++ b/artfynd/A 43083-2025 artfynd.xlsx
@@ -1680,10 +1680,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129169685</v>
+        <v>129165933</v>
       </c>
       <c r="B11" t="n">
-        <v>57887</v>
+        <v>57724</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1691,39 +1691,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Svarthöljsbäcken, Svarthöljsbäcken, Vstm</t>
+          <t>Rötjärnshöljan, Rötjärnshöljan, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>504320</v>
+        <v>503875</v>
       </c>
       <c r="R11" t="n">
-        <v>6643685</v>
+        <v>6643308</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1765,12 +1765,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2 st varningsläte.</t>
+          <t>Födohack av spillkråka på stående grov död tall.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1797,10 +1797,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129165933</v>
+        <v>129169685</v>
       </c>
       <c r="B12" t="n">
-        <v>57724</v>
+        <v>57887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1808,39 +1808,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Rötjärnshöljan, Rötjärnshöljan, Vstm</t>
+          <t>Svarthöljsbäcken, Svarthöljsbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>503875</v>
+        <v>504320</v>
       </c>
       <c r="R12" t="n">
-        <v>6643308</v>
+        <v>6643685</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Födohack av spillkråka på stående grov död tall.</t>
+          <t>2 st varningsläte.</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 43083-2025 artfynd.xlsx
+++ b/artfynd/A 43083-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129166636</v>
       </c>
       <c r="B2" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129167601</v>
       </c>
       <c r="B3" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>129164207</v>
       </c>
       <c r="B4" t="n">
-        <v>91517</v>
+        <v>91545</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>129167558</v>
       </c>
       <c r="B5" t="n">
-        <v>91326</v>
+        <v>91354</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>129166612</v>
       </c>
       <c r="B6" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>129167896</v>
       </c>
       <c r="B7" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>129166637</v>
       </c>
       <c r="B8" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>129166514</v>
       </c>
       <c r="B9" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>129168008</v>
       </c>
       <c r="B10" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1680,10 +1680,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129169685</v>
+        <v>129165933</v>
       </c>
       <c r="B11" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1691,39 +1691,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Svarthöljsbäcken, Svarthöljsbäcken, Vstm</t>
+          <t>Rötjärnshöljan, Rötjärnshöljan, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>504320</v>
+        <v>503875</v>
       </c>
       <c r="R11" t="n">
-        <v>6643685</v>
+        <v>6643308</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1765,12 +1765,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2 st varningsläte.</t>
+          <t>Födohack av spillkråka på stående grov död tall.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1797,10 +1797,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129165933</v>
+        <v>129169685</v>
       </c>
       <c r="B12" t="n">
-        <v>57724</v>
+        <v>57890</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1808,39 +1808,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Rötjärnshöljan, Rötjärnshöljan, Vstm</t>
+          <t>Svarthöljsbäcken, Svarthöljsbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>503875</v>
+        <v>504320</v>
       </c>
       <c r="R12" t="n">
-        <v>6643308</v>
+        <v>6643685</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Födohack av spillkråka på stående grov död tall.</t>
+          <t>2 st varningsläte.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1917,7 +1917,7 @@
         <v>129169688</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 43083-2025 artfynd.xlsx
+++ b/artfynd/A 43083-2025 artfynd.xlsx
@@ -1566,7 +1566,7 @@
         <v>129168008</v>
       </c>
       <c r="B10" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>129165933</v>
       </c>
       <c r="B11" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>129169685</v>
       </c>
       <c r="B12" t="n">
-        <v>57890</v>
+        <v>57895</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         <v>129169688</v>
       </c>
       <c r="B13" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 43083-2025 artfynd.xlsx
+++ b/artfynd/A 43083-2025 artfynd.xlsx
@@ -1566,7 +1566,7 @@
         <v>129168008</v>
       </c>
       <c r="B10" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>129165933</v>
       </c>
       <c r="B11" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>129169685</v>
       </c>
       <c r="B12" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         <v>129169688</v>
       </c>
       <c r="B13" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 43083-2025 artfynd.xlsx
+++ b/artfynd/A 43083-2025 artfynd.xlsx
@@ -1800,7 +1800,7 @@
         <v>129169685</v>
       </c>
       <c r="B12" t="n">
-        <v>57896</v>
+        <v>57895</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1826,11 +1826,14 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Svarthöljsbäcken, Svarthöljsbäcken, Vstm</t>
@@ -1883,11 +1886,6 @@
       <c r="AB12" t="inlineStr">
         <is>
           <t>13:38</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>2 st varningsläte.</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 43083-2025 artfynd.xlsx
+++ b/artfynd/A 43083-2025 artfynd.xlsx
@@ -1800,7 +1800,7 @@
         <v>129169685</v>
       </c>
       <c r="B12" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 43083-2025 artfynd.xlsx
+++ b/artfynd/A 43083-2025 artfynd.xlsx
@@ -1800,7 +1800,7 @@
         <v>129169685</v>
       </c>
       <c r="B12" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 43083-2025 artfynd.xlsx
+++ b/artfynd/A 43083-2025 artfynd.xlsx
@@ -1800,7 +1800,7 @@
         <v>129169685</v>
       </c>
       <c r="B12" t="n">
-        <v>57900</v>
+        <v>57985</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
